--- a/V9_W8_B32/data_instructions/VLIW_Excel/Unit18_PosP.xlsx
+++ b/V9_W8_B32/data_instructions/VLIW_Excel/Unit18_PosP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V7\data_instructions\VLIW_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V9_W8_B32\data_instructions\VLIW_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B697808A-9AC2-496D-8285-D8138407975E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAB619B-A90D-401E-B879-96F91F4C1E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{92D39E35-E6AD-4D32-9F4F-66752069E36D}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{92D39E35-E6AD-4D32-9F4F-66752069E36D}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t>OP_Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -166,6 +166,10 @@
   </si>
   <si>
     <t>100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Requant_Sel[3]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -839,6 +843,9 @@
       <c r="M5" s="8" t="s">
         <v>27</v>
       </c>
+      <c r="N5" s="7" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B7" s="17"/>
